--- a/astro-site/public/dl/pastry-shop-checklist-templates/05-bakery-cleaning-schedule-maintenance-inventory.xlsx
+++ b/astro-site/public/dl/pastry-shop-checklist-templates/05-bakery-cleaning-schedule-maintenance-inventory.xlsx
@@ -1517,7 +1517,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Deep clean the oven (pyrolytic cycle or by hand with cleaners)</t>
+          <t>Deep clean the oven (self-clean cycle if your oven has one, or by hand with oven cleaner)</t>
         </is>
       </c>
       <c r="C6" s="26" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Check walk-in drains</t>
+          <t>Check walk-in drains; pest control: check traps and entry points and file the pest control operator's report</t>
         </is>
       </c>
       <c r="C15" s="26" t="inlineStr">
